--- a/reports/2026-07-29/blotter_report.xlsx
+++ b/reports/2026-07-29/blotter_report.xlsx
@@ -944,7 +944,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-29 07:20:10.307919+00:00</t>
+          <t>2026-07-29 07:23:26.464232+00:00</t>
         </is>
       </c>
     </row>
@@ -966,7 +966,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-29 07:20:10.307919+00:00</t>
+          <t>2026-06-29 07:23:26.464232+00:00</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FAILED fetched=0 truncated=False Socrata fetch failed for fdj4-gpfu: HTTP 400 for https://data.austintexas.gov/resource/fdj4-gpfu.json?%24where=latitude+between+30.39270168394081+and+30.410688116059188+AND+longitude+between+-97.73691453289148+and+-97.71606066710852+AND+occ_date+%3E+%272026-06-29T07%3A20%3A10%27&amp;%24limit=5000&amp;%24order=occ_date+DESC :: {"message":"Query coordinator error: query.soql.no-such-column; No such column: latitude; position: Map(row -&gt; 1, column -&gt; 325, line -&gt; \"SELECT `incident_report_number`, `crime_type`, `ucr_code`, `family_violence`, `occ_date_time`, `occ_date`, `occ_time`, `rep_date_time`, `rep_date`, `rep_time`, `</t>
+          <t>FAILED fetched=0 truncated=False Socrata fetch failed for fdj4-gpfu: HTTP 400 for https://data.austintexas.gov/resource/fdj4-gpfu.json?%24where=latitude+between+30.39270168394081+and+30.410688116059188+AND+longitude+between+-97.73691453289148+and+-97.71606066710852+AND+occ_date+%3E+%272026-06-29T07%3A23%3A26%27&amp;%24limit=5000&amp;%24order=occ_date+DESC :: {"message":"Query coordinator error: query.soql.no-such-column; No such column: latitude; position: Map(row -&gt; 1, column -&gt; 325, line -&gt; \"SELECT `incident_report_number`, `crime_type`, `ucr_code`, `family_violence`, `occ_date_time`, `occ_date`, `occ_time`, `rep_date_time`, `rep_date`, `rep_time`, `</t>
         </is>
       </c>
     </row>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>FAILED fetched=0 truncated=False Socrata fetch failed for tazs-3rd5: HTTP 400 for https://data.seattle.gov/resource/tazs-3rd5.json?%24where=latitude+between+47.69905138394081+and+47.71703781605919+AND+longitude+between+-122.33973349064095+and+-122.31300410935904+AND+offense_start_datetime+%3E+%272026-06-29T07%3A20%3A10%27&amp;%24limit=5000&amp;%24order=offense_start_datetime+DESC :: {"message":"Query coordinator error: query.soql.no-such-column; No such column: offense_start_datetime; position: Map(row -&gt; 1, column -&gt; 513, line -&gt; \"SELECT `report_number`, `report_date_time`, `offense_id`, `offense_date`, `nibrs_group_a_b`, `nibrs_crime_against_category`, `offense_sub_category`</t>
+          <t>FAILED fetched=0 truncated=False Socrata fetch failed for tazs-3rd5: HTTP 400 for https://data.seattle.gov/resource/tazs-3rd5.json?%24where=latitude+between+47.69905138394081+and+47.71703781605919+AND+longitude+between+-122.33973349064095+and+-122.31300410935904+AND+offense_start_datetime+%3E+%272026-06-29T07%3A23%3A26%27&amp;%24limit=5000&amp;%24order=offense_start_datetime+DESC :: {"message":"Query coordinator error: query.soql.no-such-column; No such column: offense_start_datetime; position: Map(row -&gt; 1, column -&gt; 513, line -&gt; \"SELECT `report_number`, `report_date_time`, `offense_id`, `offense_date`, `nibrs_group_a_b`, `nibrs_crime_against_category`, `offense_sub_category`</t>
         </is>
       </c>
     </row>

--- a/reports/2026-07-29/blotter_report.xlsx
+++ b/reports/2026-07-29/blotter_report.xlsx
@@ -944,7 +944,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-29 07:23:26.464232+00:00</t>
+          <t>2026-07-29 07:26:39.565963+00:00</t>
         </is>
       </c>
     </row>
@@ -966,7 +966,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-29 07:23:26.464232+00:00</t>
+          <t>2026-06-29 07:26:39.565963+00:00</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FAILED fetched=0 truncated=False Socrata fetch failed for fdj4-gpfu: HTTP 400 for https://data.austintexas.gov/resource/fdj4-gpfu.json?%24where=latitude+between+30.39270168394081+and+30.410688116059188+AND+longitude+between+-97.73691453289148+and+-97.71606066710852+AND+occ_date+%3E+%272026-06-29T07%3A23%3A26%27&amp;%24limit=5000&amp;%24order=occ_date+DESC :: {"message":"Query coordinator error: query.soql.no-such-column; No such column: latitude; position: Map(row -&gt; 1, column -&gt; 325, line -&gt; \"SELECT `incident_report_number`, `crime_type`, `ucr_code`, `family_violence`, `occ_date_time`, `occ_date`, `occ_time`, `rep_date_time`, `rep_date`, `rep_time`, `</t>
+          <t>FAILED fetched=0 truncated=False Socrata fetch failed for fdj4-gpfu: HTTP 400 for https://data.austintexas.gov/resource/fdj4-gpfu.json?%24where=latitude+between+30.39270168394081+and+30.410688116059188+AND+longitude+between+-97.73691453289148+and+-97.71606066710852+AND+occ_date+%3E+%272026-06-29T07%3A26%3A39%27&amp;%24limit=5000&amp;%24order=occ_date+DESC :: {"message":"Query coordinator error: query.soql.no-such-column; No such column: latitude; position: Map(row -&gt; 1, column -&gt; 325, line -&gt; \"SELECT `incident_report_number`, `crime_type`, `ucr_code`, `family_violence`, `occ_date_time`, `occ_date`, `occ_time`, `rep_date_time`, `rep_date`, `rep_time`, `</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>FAILED fetched=0 truncated=False Socrata fetch failed for 2u6v-ujjs: Non-JSON response from https://hub.arcgis.com/legacy :: &lt;!DOCTYPE html&gt; &lt;!--[if lt IE 9]&gt; &lt;html class="ie lt-ie9 ie8"&gt; &lt;![endif]--&gt; &lt;!--[if IE 9]&gt; &lt;html class="ie ie9"&gt; &lt;![endif]--&gt; &lt;!--[if !IE]&gt;&lt;!--&gt; &lt;html&gt; &lt;!--&lt;![endif]--&gt; &lt;head&gt; &lt;meta charset="UT</t>
+          <t>FAILED fetched=0 truncated=False ArcGIS error for Metro Nashville PD Incidents: {'code': 400, 'message': 'Cannot perform query. Invalid query parameters.', 'details': ['Unable to perform query. Please check your parameters.']}</t>
         </is>
       </c>
     </row>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>FAILED fetched=0 truncated=False Socrata fetch failed for tazs-3rd5: HTTP 400 for https://data.seattle.gov/resource/tazs-3rd5.json?%24where=latitude+between+47.69905138394081+and+47.71703781605919+AND+longitude+between+-122.33973349064095+and+-122.31300410935904+AND+offense_start_datetime+%3E+%272026-06-29T07%3A23%3A26%27&amp;%24limit=5000&amp;%24order=offense_start_datetime+DESC :: {"message":"Query coordinator error: query.soql.no-such-column; No such column: offense_start_datetime; position: Map(row -&gt; 1, column -&gt; 513, line -&gt; \"SELECT `report_number`, `report_date_time`, `offense_id`, `offense_date`, `nibrs_group_a_b`, `nibrs_crime_against_category`, `offense_sub_category`</t>
+          <t>FAILED fetched=0 truncated=False Socrata fetch failed for tazs-3rd5: HTTP 400 for https://data.seattle.gov/resource/tazs-3rd5.json?%24where=latitude%3A%3Anumber+between+47.69905138394081+and+47.71703781605919+AND+longitude%3A%3Anumber+between+-122.33973349064095+and+-122.31300410935904+AND+offense_date+%3E+%272026-06-29T07%3A26%3A39%27&amp;%24limit=5000&amp;%24order=offense_date+DESC :: {"message":"Query coordinator error: 400; ERROR: invalid input syntax for type numeric: \"REDACTED\"","errorCode":"400","data":{"source":"soql-server"}}</t>
         </is>
       </c>
     </row>

--- a/reports/2026-07-29/blotter_report.xlsx
+++ b/reports/2026-07-29/blotter_report.xlsx
@@ -14,8 +14,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$K$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Highlights'!$A$1:$L$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All Incidents'!$A$1:$L$178</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Highlights'!$A$1:$M$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'All Incidents'!$A$1:$M$178</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Run Metadata'!$A$1:$B$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -766,7 +766,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -781,6 +781,7 @@
     <col width="20" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -844,6 +845,11 @@
           <t>distance_m</t>
         </is>
       </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>synopsis</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -898,6 +904,11 @@
       <c r="L2" t="n">
         <v>145.2</v>
       </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Simple assault on Jul 22, 2026, 145 m from Northgate Station (3XX BLOCK OF NE NORTHGATE WAY). Case #2026-215149 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -952,6 +963,11 @@
       <c r="L3" t="n">
         <v>145.2</v>
       </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Robbery on Jul 21, 2026, 145 m from Northgate Station (4XX BLOCK OF NE NORTHGATE WAY). Case #2026-213187 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1006,6 +1022,11 @@
       <c r="L4" t="n">
         <v>338.4</v>
       </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Simple assault on Jul 07, 2026, 338 m from Northgate Station (5XX BLOCK OF NE NORTHGATE WAY). Case #2026-196771 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1060,6 +1081,11 @@
       <c r="L5" t="n">
         <v>497.7</v>
       </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Robbery-bank on Jul 01, 2026, 498 m from Cherry Creek Shopping Center (3410 E 1ST AVE). Victims: 1. Case #DP2026357948 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1114,6 +1140,11 @@
       <c r="L6" t="n">
         <v>539</v>
       </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Weapon law violations on Jul 17, 2026, 539 m from Northgate Station (8XX BLOCK OF NE NORTHGATE WAY). Case #2026-208823 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1168,6 +1199,11 @@
       <c r="L7" t="n">
         <v>566.4</v>
       </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Assault-simple on Jul 22, 2026, 566 m from Cherry Creek Shopping Center (300 BLOCK N ST PAUL ST). Victims: 1. Case #DP2026403380 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1222,6 +1258,11 @@
       <c r="L8" t="n">
         <v>596.2</v>
       </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Robbery on Jul 11, 2026, 596 m from Northgate Station (5TH AVE NE / NE 103RD ST). Case #2026-202517 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1276,6 +1317,11 @@
       <c r="L9" t="n">
         <v>639.8</v>
       </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Weapon law violations on Jul 11, 2026, 640 m from Northgate Station (ROOSEVELT WAY NE / NE NORTHGATE WAY). Case #2026-202517 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1330,6 +1376,11 @@
       <c r="L10" t="n">
         <v>798.3</v>
       </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Aggravated assault on Jul 02, 2026, 798 m from Northgate Station (117XX BLOCK OF 5TH AVE NE). Case #2026-191308 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1380,6 +1431,11 @@
       <c r="L11" t="n">
         <v>808.3</v>
       </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Assault- fear of bodily injury on Jul 11, 2026, 808 m from Opry Mills (OPRYLAND). Premises: HOTEL, MOTEL, ETC.. Status: OPEN. Victims: 1. Case #20260423135 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1434,6 +1490,11 @@
       <c r="L12" t="n">
         <v>936.3</v>
       </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Assault, aggravated - deadly weapon - int/kn on Jul 19, 2026, 936 m from Opry Mills (2902 2902). Weapon: HANDGUN. Premises: RESIDENCE, HOME. Status: CLEARED BY ARREST. Victims: 1. Flags: domestic related. Case #20260440008 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1488,6 +1549,11 @@
       <c r="L13" t="n">
         <v>936.3</v>
       </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Assault- offensive or provocative contact on Jul 19, 2026, 936 m from Opry Mills (2902 2902). Weapon: PERSONAL (HANDS). Premises: RESIDENCE, HOME. Status: CLEARED BY ARREST. Victims: 2. Case #20260440008 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1542,6 +1608,11 @@
       <c r="L14" t="n">
         <v>936.3</v>
       </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Weapon offense, criminal attempt on Jul 19, 2026, 936 m from Opry Mills (2902 2902). Weapon: HANDGUN. Premises: RESIDENCE, HOME. Status: CLEARED BY ARREST. Victims: 3. Case #20260440008 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1596,6 +1667,11 @@
       <c r="L15" t="n">
         <v>25.7</v>
       </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Theft-shoplift on Jul 21, 2026, 26 m from Cherry Creek Shopping Center (3000 E 1ST AVE). Victims: 1. Case #DP20266009882 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1650,6 +1726,11 @@
       <c r="L16" t="n">
         <v>25.7</v>
       </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Theft-from-bldg on Jul 15, 2026, 26 m from Cherry Creek Shopping Center (3000 E 1ST AVE). Victims: 1. Case #DP20266009631 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1704,6 +1785,11 @@
       <c r="L17" t="n">
         <v>25.7</v>
       </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Theft-shoplift on Jul 09, 2026, 26 m from Cherry Creek Shopping Center (3000 E 1ST AVE). Victims: 1. Case #DP20266009395 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1758,6 +1844,11 @@
       <c r="L18" t="n">
         <v>25.7</v>
       </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Theft-shoplift on Jul 09, 2026, 26 m from Cherry Creek Shopping Center (3000 E 1ST AVE). Victims: 1. Case #DP2026380800 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1812,6 +1903,11 @@
       <c r="L19" t="n">
         <v>25.7</v>
       </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Theft-shoplift on Jul 08, 2026, 26 m from Cherry Creek Shopping Center (3000 E 1ST AVE). Victims: 1. Case #DP2026376323 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1866,6 +1962,11 @@
       <c r="L20" t="n">
         <v>25.7</v>
       </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Theft-shoplift on Jul 05, 2026, 26 m from Cherry Creek Shopping Center (3000 E 1ST AVE). Victims: 1. Case #DP20266009170 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1920,6 +2021,11 @@
       <c r="L21" t="n">
         <v>25.7</v>
       </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Theft-shoplift on Jul 02, 2026, 26 m from Cherry Creek Shopping Center (3000 E 1ST AVE). Victims: 1. Case #DP20266009209 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1974,6 +2080,11 @@
       <c r="L22" t="n">
         <v>25.7</v>
       </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Theft-shoplift on Jun 29, 2026, 26 m from Cherry Creek Shopping Center (3000 E 1ST AVE). Victims: 1. Case #DP20266008929 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2028,6 +2139,11 @@
       <c r="L23" t="n">
         <v>100.4</v>
       </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Theft-other on Jul 20, 2026, 100 m from Cherry Creek Shopping Center (3030 E 1ST AVE). Victims: 1. Case #DP2026399148 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2078,6 +2194,11 @@
       <c r="L24" t="n">
         <v>111.8</v>
       </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>594(b)(1) - pc - f - vandalism ($400 or more) - felony - 290 on Jul 04, 2026, 112 m from Beverly Center (8500 W Beverly Blvd). Premises: Parking Lot / Garage / Drop Lot. Status: Open. Victims: 1. Case #C269028320 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2132,6 +2253,11 @@
       <c r="L25" t="n">
         <v>113.7</v>
       </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 24, 2026, 114 m from Opry Mills (211 211). Premises: DEPARTMENT, DISCOUNT STORE. Status: CLEARED BY ARREST. Victims: 1. Case #20260449995 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2186,9 +2312,14 @@
       <c r="L26" t="n">
         <v>113.7</v>
       </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 18, 2026, 114 m from Opry Mills (211 211). Premises: DEPARTMENT, DISCOUNT STORE. Status: CLEARED BY ARREST. Victims: 1. Case #20260438245 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L26"/>
+  <autoFilter ref="A1:M26"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2199,7 +2330,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L178"/>
+  <dimension ref="A1:M178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2214,6 +2345,7 @@
     <col width="20" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2277,6 +2409,11 @@
           <t>distance_m</t>
         </is>
       </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>synopsis</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2327,6 +2464,11 @@
       <c r="L2" t="n">
         <v>394.4</v>
       </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>459.5(a) - pc - m - petty theft - shoplifting - 23c on Jul 11, 2026, 394 m from Beverly Center (8400 Beverly Blvd). Premises: The Beverly Connection. Status: Open. Victims: 1. Case #C269029303 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2377,6 +2519,11 @@
       <c r="L3" t="n">
         <v>464.1</v>
       </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>459.5(a) - pc - m - petty theft - shoplifting - 23c on Jul 10, 2026, 464 m from Beverly Center (8400 W 3rd St). Premises: Department / Discount Store. Status: Open. Victims: 1. Case #C269029051 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2427,6 +2574,11 @@
       <c r="L4" t="n">
         <v>229.4</v>
       </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>459.5(a) - pc - m - petty theft - shoplifting - 23c on Jul 10, 2026, 229 m from Beverly Center (100 N La Cienega Blvd). Premises: Department / Discount Store. Status: Open. Victims: 1. Case #26134379 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2477,6 +2629,11 @@
       <c r="L5" t="n">
         <v>394.4</v>
       </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>459.5(a) - pc - m - petty theft - shoplifting - 23c on Jul 08, 2026, 394 m from Beverly Center (8400 Beverly Blvd). Premises: Other Business. Status: Open. Victims: 1. Case #26133458 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2527,6 +2684,11 @@
       <c r="L6" t="n">
         <v>394.4</v>
       </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>459.5(a) - pc - m - petty theft - shoplifting - 23c on Jul 08, 2026, 394 m from Beverly Center (8400 Beverly Blvd). Premises: Other Business. Status: Cleared by Arrest - CA Filed. Victims: 1. Case #26132960 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2577,6 +2739,11 @@
       <c r="L7" t="n">
         <v>394.4</v>
       </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>459.5(a) - pc - m - petty theft - shoplifting - 23c on Jul 08, 2026, 394 m from Beverly Center (8400 Beverly Blvd). Premises: Department / Discount Store. Status: Open. Victims: 1. Case #C269028868 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2627,6 +2794,11 @@
       <c r="L8" t="n">
         <v>229.4</v>
       </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>459.5(a) - pc - m - petty theft - shoplifting - 23c on Jul 08, 2026, 229 m from Beverly Center (100 N La Cienega Blvd). Premises: Other Business. Status: Open. Victims: 1. Case #26132830 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2677,6 +2849,11 @@
       <c r="L9" t="n">
         <v>979.6</v>
       </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>459 - pc - f - burglary - non-residential - 220 on Jul 07, 2026, 980 m from Beverly Center (8400 Melrose Pl). Premises: Clothing Store. Status: Investigation Continued. Victims: 1. Case #26131883 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2727,6 +2904,11 @@
       <c r="L10" t="n">
         <v>111.8</v>
       </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>594(b)(1) - pc - f - vandalism ($400 or more) - felony - 290 on Jul 04, 2026, 112 m from Beverly Center (8500 W Beverly Blvd). Premises: Parking Lot / Garage / Drop Lot. Status: Open. Victims: 1. Case #C269028320 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2777,6 +2959,11 @@
       <c r="L11" t="n">
         <v>394.4</v>
       </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>459.5(a) - pc - m - petty theft - shoplifting - 23c on Jul 04, 2026, 394 m from Beverly Center (8400 Beverly Blvd). Premises: Department / Discount Store. Status: Open. Victims: 1. Case #26130052 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2827,6 +3014,11 @@
       <c r="L12" t="n">
         <v>464.1</v>
       </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>459.5(a) - pc - m - petty theft - shoplifting - 23c on Jul 02, 2026, 464 m from Beverly Center (8400 W 3rd St). Premises: Department / Discount Store. Status: Investigation Continued. Victims: 1. Case #C269027969 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2877,6 +3069,11 @@
       <c r="L13" t="n">
         <v>394.4</v>
       </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>459.5(a) - pc - m - petty theft - shoplifting - 23c on Jul 01, 2026, 394 m from Beverly Center (8400 Beverly Blvd). Premises: Clothing Store. Status: Open. Victims: 1. Case #26128108 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2931,6 +3128,11 @@
       <c r="L14" t="n">
         <v>113.7</v>
       </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 18, 2026, 114 m from Opry Mills (211 211). Premises: DEPARTMENT, DISCOUNT STORE. Status: CLEARED BY ARREST. Victims: 1. Case #20260438245 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2985,6 +3187,11 @@
       <c r="L15" t="n">
         <v>113.7</v>
       </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 24, 2026, 114 m from Opry Mills (211 211). Premises: DEPARTMENT, DISCOUNT STORE. Status: CLEARED BY ARREST. Victims: 1. Case #20260449995 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3035,6 +3242,11 @@
       <c r="L16" t="n">
         <v>125.9</v>
       </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Lost property on Jul 05, 2026, 126 m from Opry Mills (433 433). Premises: Shopping Mall. Status: UNFOUNDED. Victims: 1. Case #20260411784 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3089,6 +3301,11 @@
       <c r="L17" t="n">
         <v>125.9</v>
       </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Lost property on Jul 25, 2026, 126 m from Opry Mills (433 433). Premises: Shopping Mall. Status: UNFOUNDED. Victims: 1. Case #20260451873 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3143,6 +3360,11 @@
       <c r="L18" t="n">
         <v>125.9</v>
       </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 10, 2026, 126 m from Opry Mills (433 433). Premises: DEPARTMENT, DISCOUNT STORE. Status: CLEARED BY ARREST. Victims: 1. Case #20260421984 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3197,6 +3419,11 @@
       <c r="L19" t="n">
         <v>125.9</v>
       </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Police inquiry on Jul 07, 2026, 126 m from Opry Mills (433 433). Premises: Shopping Mall. Status: UNFOUNDED. Victims: 1. Flags: domestic related. Case #20260415824 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3251,6 +3478,11 @@
       <c r="L20" t="n">
         <v>125.9</v>
       </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Theft of merchandise- $1,000 or less on Jul 09, 2026, 126 m from Opry Mills (433 433). Weapon: PERSONAL (HANDS). Premises: Shopping Mall. Status: CLEARED BY ARREST. Victims: 1. Case #20260419741 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3305,6 +3537,11 @@
       <c r="L21" t="n">
         <v>125.9</v>
       </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Theft of merchandise- $1,000 or less on Jul 09, 2026, 126 m from Opry Mills (433 433). Weapon: PERSONAL (HANDS). Premises: Shopping Mall. Status: CLEARED BY ARREST. Victims: 2. Case #20260419741 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3359,6 +3596,11 @@
       <c r="L22" t="n">
         <v>125.9</v>
       </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Theft of merchandise- $1,000 or less on Jul 09, 2026, 126 m from Opry Mills (433 433). Weapon: PERSONAL (HANDS). Premises: Shopping Mall. Status: CLEARED BY ARREST. Victims: 3. Case #20260419741 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3413,6 +3655,11 @@
       <c r="L23" t="n">
         <v>125.9</v>
       </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Theft of merchandise- $1,000 or less on Jul 09, 2026, 126 m from Opry Mills (433 433). Weapon: PERSONAL (HANDS). Premises: Shopping Mall. Status: CLEARED BY ARREST. Victims: 4. Case #20260419741 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3467,6 +3714,11 @@
       <c r="L24" t="n">
         <v>125.9</v>
       </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Possession of a controlled substance on Jul 25, 2026, 126 m from Opry Mills (433 433). Premises: SPECIALTY STORE. Status: CLEARED BY ARREST. Victims: 1. Case #20260451698 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3521,6 +3773,11 @@
       <c r="L25" t="n">
         <v>227.6</v>
       </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Theft of merchandise- $1,000 or less on Jul 19, 2026, 228 m from Opry Mills (357 357). Premises: SPECIALTY STORE. Status: CLEARED BY ARREST. Victims: 1. Case #20260439763 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3575,6 +3832,11 @@
       <c r="L26" t="n">
         <v>271</v>
       </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Lost property on Jul 12, 2026, 271 m from Opry Mills (550 550). Premises: Shopping Mall. Status: UNFOUNDED. Victims: 1. Case #20260424643 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3629,6 +3891,11 @@
       <c r="L27" t="n">
         <v>338.4</v>
       </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Theft of merchandise- $1,000 or less on Jul 19, 2026, 338 m from Opry Mills (428 428). Premises: SPECIALTY STORE. Status: Closed. Victims: 1. Case #20260439850 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3683,6 +3950,11 @@
       <c r="L28" t="n">
         <v>343.9</v>
       </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Harrassment (nuisance) on Jul 03, 2026, 344 m from Opry Mills (353 353). Premises: RESIDENCE, HOME. Status: REFUSED TO COOPERATE. Victims: 1. Flags: domestic related. Case #20260407934 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3737,6 +4009,11 @@
       <c r="L29" t="n">
         <v>387.3</v>
       </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Theft of merchandise 5th - $1,000 or less on Jul 04, 2026, 387 m from Opry Mills (OPRY MILLS). Weapon: PERSONAL (HANDS). Premises: SPECIALTY STORE. Status: OPEN. Victims: 1. Case #20260411424 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3791,6 +4068,11 @@
       <c r="L30" t="n">
         <v>387.3</v>
       </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Vehicle theft on Jul 05, 2026, 387 m from Opry Mills (OPRY MILLS). Premises: PARKING LOT, GARAGE. Status: OPEN. Victims: 1. Case #20260411660 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3845,6 +4127,11 @@
       <c r="L31" t="n">
         <v>387.3</v>
       </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Larc - from bldg on Jul 13, 2026, 387 m from Opry Mills (OPRY MILLS DR). Premises: DEPARTMENT, DISCOUNT STORE. Status: OPEN. Victims: 1. Case #20260427548 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3899,6 +4186,11 @@
       <c r="L32" t="n">
         <v>387.3</v>
       </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Larc - from bldg on Jul 05, 2026, 387 m from Opry Mills (OPRY MILLS DR). Weapon: PERSONAL (HANDS). Premises: SPECIALTY STORE. Status: OPEN. Victims: 1. Case #20260411259 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3953,6 +4245,11 @@
       <c r="L33" t="n">
         <v>387.3</v>
       </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 02, 2026, 387 m from Opry Mills (OPRY MILLS DR). Weapon: PERSONAL (HANDS). Premises: Shopping Mall. Status: OPEN. Victims: 1. Case #20260405842 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -4007,6 +4304,11 @@
       <c r="L34" t="n">
         <v>387.3</v>
       </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Fraud -  illeg use of credit cards on Jul 06, 2026, 387 m from Opry Mills (OPRY MILLS). Weapon: PERSONAL (HANDS). Premises: SPECIALTY STORE. Status: OPEN. Victims: 1. Case #20260423957 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4061,6 +4363,11 @@
       <c r="L35" t="n">
         <v>387.3</v>
       </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Damage prop - private on Jul 21, 2026, 387 m from Opry Mills (OPRY MILLS DR). Weapon: Unarmed. Premises: PARKING LOT, GARAGE. Status: OPEN. Victims: 1. Case #20260443304 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4115,6 +4422,11 @@
       <c r="L36" t="n">
         <v>387.3</v>
       </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 13, 2026, 387 m from Opry Mills (OPRY MILLS DR). Premises: SPECIALTY STORE. Status: OPEN. Victims: 1. Case #20260427787 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4169,6 +4481,11 @@
       <c r="L37" t="n">
         <v>387.3</v>
       </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Larc - from bldg on Jul 03, 2026, 387 m from Opry Mills (OPRY MILLS DR). Premises: SPECIALTY STORE. Status: OPEN. Victims: 1. Case #20260407874 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4223,6 +4540,11 @@
       <c r="L38" t="n">
         <v>387.3</v>
       </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Credit card, fraudulent use - $1,000 or less on Jul 09, 2026, 387 m from Opry Mills (OPRY MILLS DR). Premises: Shopping Mall. Status: OPEN. Victims: 1. Case #20260419743 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4277,6 +4599,11 @@
       <c r="L39" t="n">
         <v>441.5</v>
       </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 22, 2026, 442 m from Opry Mills (211 211). Premises: SPECIALTY STORE. Status: CLEARED BY ARREST. Victims: 1. Case #20260445712 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4331,6 +4658,11 @@
       <c r="L40" t="n">
         <v>474.9</v>
       </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Theft of merchandise 5th - $1,000 or less on Jul 16, 2026, 475 m from Opry Mills (323 323). Weapon: PERSONAL (HANDS). Premises: SPECIALTY STORE. Status: CLEARED BY ARREST. Victims: 1. Case #20260434111 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4385,6 +4717,11 @@
       <c r="L41" t="n">
         <v>525.5</v>
       </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Simple asslt on Jul 11, 2026, 526 m from Opry Mills (3725 3725). Weapon: PERSONAL (HANDS). Premises: RESIDENCE, HOME. Status: CLEARED BY ARREST. Victims: 1. Flags: domestic related. Case #20260423835 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4439,6 +4776,11 @@
       <c r="L42" t="n">
         <v>688.9</v>
       </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Police inquiry on Jul 11, 2026, 689 m from Opry Mills (211 211). Premises: PARKING LOT, GARAGE. Status: UNFOUNDED. Victims: 1. Case #20260424550 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4493,6 +4835,11 @@
       <c r="L43" t="n">
         <v>768.3</v>
       </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Fraud -  illeg use of credit cards on Jul 21, 2026, 768 m from Opry Mills (MORGANMEADE DR). Premises: RESIDENCE, HOME. Status: OPEN. Victims: 1. Case #20260443720 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4547,6 +4894,11 @@
       <c r="L44" t="n">
         <v>768.3</v>
       </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Larc - from bldg on Jul 25, 2026, 768 m from Opry Mills (OPRY MILLS). Premises: RESTAURANT. Status: OPEN. Victims: 1. Case #20260451780 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4601,6 +4953,11 @@
       <c r="L45" t="n">
         <v>808.3</v>
       </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 25, 2026, 808 m from Opry Mills (OPRY MILLS DR). Premises: SPECIALTY STORE. Status: OPEN. Victims: 1. Case #20260451462 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4655,6 +5012,11 @@
       <c r="L46" t="n">
         <v>808.3</v>
       </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Theft of property-&gt;$1,000 but &lt;$2,500 on Jul 10, 2026, 808 m from Opry Mills (OPRYLAND DR). Weapon: Unarmed. Premises: PARK. Status: OPEN. Victims: 1. Case #20260421200 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4709,6 +5071,11 @@
       <c r="L47" t="n">
         <v>808.3</v>
       </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 01, 2026, 808 m from Opry Mills (OPRY MILLS DR). Premises: SPECIALTY STORE. Status: OPEN. Victims: 1. Case #20260403493 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4759,6 +5126,11 @@
       <c r="L48" t="n">
         <v>808.3</v>
       </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>Vehicle theft on Jul 08, 2026, 808 m from Opry Mills (OPRYLAND DR). Premises: HOTEL, MOTEL, ETC.. Status: OPEN. Victims: 1. Case #20260425948 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -4813,6 +5185,11 @@
       <c r="L49" t="n">
         <v>808.3</v>
       </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>Larc - from bldg on Jul 09, 2026, 808 m from Opry Mills (OPRYLAND DR). Premises: HOTEL, MOTEL, ETC.. Status: OPEN. Victims: 1. Case #20260418604 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -4867,6 +5244,11 @@
       <c r="L50" t="n">
         <v>808.3</v>
       </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 06, 2026, 808 m from Opry Mills (OPRY MILLS DR). Premises: SPECIALTY STORE. Status: OPEN. Victims: 1. Case #20260413875 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -4921,6 +5303,11 @@
       <c r="L51" t="n">
         <v>808.3</v>
       </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Burglary- motor vehicle on Jun 29, 2026, 808 m from Opry Mills (OPRY MILLS DR). Premises: PARKING LOT, GARAGE. Status: OPEN. Victims: 1. Case #20260399283 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -4975,6 +5362,11 @@
       <c r="L52" t="n">
         <v>808.3</v>
       </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>Theft of property- $10,000 or &gt;  but  &lt; $60,000 on Jul 02, 2026, 808 m from Opry Mills (OPRYLAND DR). Premises: PARKING LOT, GARAGE. Status: OPEN. Victims: 1. Case #20260413013 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -5029,6 +5421,11 @@
       <c r="L53" t="n">
         <v>808.3</v>
       </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 27, 2026, 808 m from Opry Mills (OPRY MILLS DR). Premises: DEPARTMENT, DISCOUNT STORE. Status: OPEN. Victims: 1. Case #20260455357 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -5079,6 +5476,11 @@
       <c r="L54" t="n">
         <v>808.3</v>
       </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>Assault- fear of bodily injury on Jul 11, 2026, 808 m from Opry Mills (OPRYLAND). Premises: HOTEL, MOTEL, ETC.. Status: OPEN. Victims: 1. Case #20260423135 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -5133,6 +5535,11 @@
       <c r="L55" t="n">
         <v>808.3</v>
       </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>Larc - from bldg on Jul 06, 2026, 808 m from Opry Mills (OPRYLAND DR). Premises: Shopping Mall. Status: OPEN. Victims: 1. Case #20260419567 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -5187,6 +5594,11 @@
       <c r="L56" t="n">
         <v>808.3</v>
       </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>Criminal impersonation on Jun 29, 2026, 808 m from Opry Mills (OPRYLAND DR). Premises: COMMERCIAL, OFFICE BUILDING. Status: OPEN. Victims: 1. Case #20260434024 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -5241,6 +5653,11 @@
       <c r="L57" t="n">
         <v>808.3</v>
       </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>Fraud -  illeg use of credit cards on Jul 06, 2026, 808 m from Opry Mills (OPRY MILLS DR). Weapon: PERSONAL (HANDS). Premises: Shopping Mall. Status: OPEN. Victims: 1. Case #20260423950 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -5295,6 +5712,11 @@
       <c r="L58" t="n">
         <v>808.3</v>
       </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>Theft of merchandise- $1,000 or less on Jul 07, 2026, 808 m from Opry Mills (OPRY MILLS DR). Premises: SPECIALTY STORE. Status: OPEN. Victims: 1. Case #20260415793 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -5349,6 +5771,11 @@
       <c r="L59" t="n">
         <v>936.3</v>
       </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>Assault, aggravated - deadly weapon - int/kn on Jul 19, 2026, 936 m from Opry Mills (2902 2902). Weapon: HANDGUN. Premises: RESIDENCE, HOME. Status: CLEARED BY ARREST. Victims: 1. Flags: domestic related. Case #20260440008 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -5403,6 +5830,11 @@
       <c r="L60" t="n">
         <v>936.3</v>
       </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>Assault- offensive or provocative contact on Jul 19, 2026, 936 m from Opry Mills (2902 2902). Weapon: PERSONAL (HANDS). Premises: RESIDENCE, HOME. Status: CLEARED BY ARREST. Victims: 2. Case #20260440008 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -5457,6 +5889,11 @@
       <c r="L61" t="n">
         <v>936.3</v>
       </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>Weapon offense, criminal attempt on Jul 19, 2026, 936 m from Opry Mills (2902 2902). Weapon: HANDGUN. Premises: RESIDENCE, HOME. Status: CLEARED BY ARREST. Victims: 3. Case #20260440008 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -5511,6 +5948,11 @@
       <c r="L62" t="n">
         <v>563</v>
       </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>Burglary/breaking &amp; entering on Jul 24, 2026, 563 m from Northgate Station (113XX BLOCK OF CORLISS AVE N). Case #2026-216739 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -5565,6 +6007,11 @@
       <c r="L63" t="n">
         <v>880.9</v>
       </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>Drug/narcotic violations on Jul 23, 2026, 881 m from Northgate Station (100XX BLOCK OF COLLEGE WAY N). Case #2026-216408 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -5619,6 +6066,11 @@
       <c r="L64" t="n">
         <v>145.2</v>
       </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>Simple assault on Jul 22, 2026, 145 m from Northgate Station (3XX BLOCK OF NE NORTHGATE WAY). Case #2026-215149 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -5673,6 +6125,11 @@
       <c r="L65" t="n">
         <v>475.1</v>
       </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>All other offenses on Jul 22, 2026, 475 m from Northgate Station (21XX BLOCK OF N NORTHGATE WAY). Case #2026-215020 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -5727,6 +6184,11 @@
       <c r="L66" t="n">
         <v>812.7</v>
       </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>All other larceny on Jul 21, 2026, 813 m from Northgate Station (115XX BLOCK OF MERIDIAN AVE N). Case #2026-913058 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -5781,6 +6243,11 @@
       <c r="L67" t="n">
         <v>145.2</v>
       </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>Robbery on Jul 21, 2026, 145 m from Northgate Station (4XX BLOCK OF NE NORTHGATE WAY). Case #2026-213187 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -5835,6 +6302,11 @@
       <c r="L68" t="n">
         <v>867.4</v>
       </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>All other larceny on Jul 20, 2026, 867 m from Northgate Station (97XX BLOCK OF 3RD AVE NE). Case #2026-913061 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -5889,6 +6361,11 @@
       <c r="L69" t="n">
         <v>539</v>
       </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 20, 2026, 539 m from Northgate Station (8XX BLOCK OF NE NORTHGATE WAY). Case #2026-212215 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -5943,6 +6420,11 @@
       <c r="L70" t="n">
         <v>744.2</v>
       </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>Theft from motor vehicle on Jul 20, 2026, 744 m from Northgate Station (MERIDIAN AVE N / N 115TH ST). Case #2026-913040 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -5997,6 +6479,11 @@
       <c r="L71" t="n">
         <v>475.1</v>
       </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>Theft from building on Jul 20, 2026, 475 m from Northgate Station (21XX BLOCK OF N NORTHGATE WAY). Case #2026-211165 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -6051,6 +6538,11 @@
       <c r="L72" t="n">
         <v>145.2</v>
       </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>Motor vehicle theft on Jul 19, 2026, 145 m from Northgate Station (3XX BLOCK OF NE NORTHGATE WAY). Case #2026-211277 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -6105,6 +6597,11 @@
       <c r="L73" t="n">
         <v>648.8</v>
       </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>All other larceny on Jul 19, 2026, 649 m from Northgate Station (110XX BLOCK OF ROOSEVELT WAY NE). Case #2026-211080 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -6159,6 +6656,11 @@
       <c r="L74" t="n">
         <v>993.9</v>
       </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>Theft from motor vehicle on Jul 17, 2026, 994 m from Northgate Station (3XX BLOCK OF NE 97TH ST). Case #2026-912809 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -6213,6 +6715,11 @@
       <c r="L75" t="n">
         <v>539.1</v>
       </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>All other offenses on Jul 17, 2026, 539 m from Northgate Station (8XX BLOCK OF NE NORTHGATE WAY). Case #2026-208823 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -6267,6 +6774,11 @@
       <c r="L76" t="n">
         <v>539</v>
       </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>Weapon law violations on Jul 17, 2026, 539 m from Northgate Station (8XX BLOCK OF NE NORTHGATE WAY). Case #2026-208823 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -6321,6 +6833,11 @@
       <c r="L77" t="n">
         <v>539</v>
       </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>Not reportable to nibrs on Jul 17, 2026, 539 m from Northgate Station (8XX BLOCK OF NE NORTHGATE WAY). Case #2026-208823 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -6375,6 +6892,11 @@
       <c r="L78" t="n">
         <v>539</v>
       </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>Drug/narcotic violations on Jul 17, 2026, 539 m from Northgate Station (8XX BLOCK OF NE NORTHGATE WAY). Case #2026-208823 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -6429,6 +6951,11 @@
       <c r="L79" t="n">
         <v>539.1</v>
       </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>Not reportable to nibrs on Jul 17, 2026, 539 m from Northgate Station (8XX BLOCK OF NE NORTHGATE WAY). Case #2026-208823 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -6483,6 +7010,11 @@
       <c r="L80" t="n">
         <v>539</v>
       </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>Stolen property offenses on Jul 17, 2026, 539 m from Northgate Station (8XX BLOCK OF NE NORTHGATE WAY). Case #2026-208823 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -6537,6 +7069,11 @@
       <c r="L81" t="n">
         <v>539</v>
       </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 17, 2026, 539 m from Northgate Station (8XX BLOCK OF NE NORTHGATE WAY). Case #2026-208823 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -6591,6 +7128,11 @@
       <c r="L82" t="n">
         <v>608.3</v>
       </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>Driving under the influence on Jul 16, 2026, 608 m from Northgate Station (115XX BLOCK OF 5TH AVE NE). Case #2026-208431 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -6645,6 +7187,11 @@
       <c r="L83" t="n">
         <v>608.3</v>
       </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>Destruction/damage/vandalism of property on Jul 16, 2026, 608 m from Northgate Station (115XX BLOCK OF 5TH AVE NE). Case #2026-208431 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -6699,6 +7246,11 @@
       <c r="L84" t="n">
         <v>539</v>
       </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 16, 2026, 539 m from Northgate Station (8XX BLOCK OF NE NORTHGATE WAY). Case #2026-207596 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -6753,6 +7305,11 @@
       <c r="L85" t="n">
         <v>695.6</v>
       </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>Destruction/damage/vandalism of property on Jul 16, 2026, 696 m from Northgate Station (112XX BLOCK OF ROOSEVELT WAY NE). Case #2026-207746 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -6807,6 +7364,11 @@
       <c r="L86" t="n">
         <v>661.7</v>
       </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>All other larceny on Jul 16, 2026, 662 m from Northgate Station (102XX BLOCK OF 1ST AVE NE). Case #2026-912691 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -6861,6 +7423,11 @@
       <c r="L87" t="n">
         <v>539.1</v>
       </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 15, 2026, 539 m from Northgate Station (8XX BLOCK OF NE NORTHGATE WAY). Case #2026-207228 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -6915,6 +7482,11 @@
       <c r="L88" t="n">
         <v>627</v>
       </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>Burglary/breaking &amp; entering on Jul 15, 2026, 627 m from Northgate Station (3XX BLOCK OF NE THORNTON PL). Case #2026-912675 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -6969,6 +7541,11 @@
       <c r="L89" t="n">
         <v>694.1</v>
       </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>Wire fraud on Jul 15, 2026, 694 m from Northgate Station (112XX BLOCK OF ROOSEVELT WAY NE). Case #2026-209244 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -7023,6 +7600,11 @@
       <c r="L90" t="n">
         <v>695.6</v>
       </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>Extortion/blackmail on Jul 15, 2026, 696 m from Northgate Station (112XX BLOCK OF ROOSEVELT WAY NE). Case #2026-209244 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -7077,6 +7659,11 @@
       <c r="L91" t="n">
         <v>747.8</v>
       </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>Not reportable to nibrs on Jul 14, 2026, 748 m from Northgate Station (N NORTHGATE WAY / N 107TH ST). Case #2026-205997 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -7131,6 +7718,11 @@
       <c r="L92" t="n">
         <v>747.8</v>
       </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>All other larceny on Jul 14, 2026, 748 m from Northgate Station (N NORTHGATE WAY / N 107TH ST). Case #2026-205997 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -7185,6 +7777,11 @@
       <c r="L93" t="n">
         <v>539.1</v>
       </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 14, 2026, 539 m from Northgate Station (8XX BLOCK OF NE NORTHGATE WAY). Case #2026-205238 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -7239,6 +7836,11 @@
       <c r="L94" t="n">
         <v>446.4</v>
       </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>Theft from building on Jul 12, 2026, 446 m from Northgate Station (106XX BLOCK OF 8TH AVE NE). Case #2026-912472 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -7293,6 +7895,11 @@
       <c r="L95" t="n">
         <v>661.7</v>
       </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>Not reportable to nibrs on Jul 12, 2026, 662 m from Northgate Station (102XX BLOCK OF 1ST AVE NE). Case #2026-203277 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -7347,6 +7954,11 @@
       <c r="L96" t="n">
         <v>338.4</v>
       </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>Theft from building on Jul 12, 2026, 338 m from Northgate Station (5XX BLOCK OF NE NORTHGATE WAY). Case #2026-912560 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -7401,6 +8013,11 @@
       <c r="L97" t="n">
         <v>574.6</v>
       </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>All other offenses on Jul 11, 2026, 575 m from Northgate Station (MERIDIAN AVE N / N NORTHGATE WAY). Case #2026-202634 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -7455,6 +8072,11 @@
       <c r="L98" t="n">
         <v>639.8</v>
       </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>Weapon law violations on Jul 11, 2026, 640 m from Northgate Station (ROOSEVELT WAY NE / NE NORTHGATE WAY). Case #2026-202517 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -7509,6 +8131,11 @@
       <c r="L99" t="n">
         <v>639.8</v>
       </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>All other offenses on Jul 11, 2026, 640 m from Northgate Station (ROOSEVELT WAY NE / NE NORTHGATE WAY). Case #2026-202517 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -7563,6 +8190,11 @@
       <c r="L100" t="n">
         <v>596.2</v>
       </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>Robbery on Jul 11, 2026, 596 m from Northgate Station (5TH AVE NE / NE 103RD ST). Case #2026-202517 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -7617,6 +8249,11 @@
       <c r="L101" t="n">
         <v>680.6</v>
       </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>Motor vehicle theft on Jul 11, 2026, 681 m from Northgate Station (N 116TH ST / CORLISS AVE N). Case #2026-202934 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -7671,6 +8308,11 @@
       <c r="L102" t="n">
         <v>957.9</v>
       </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>Motor vehicle theft on Jul 11, 2026, 958 m from Northgate Station (95XX BLOCK OF 1ST AVE NE). Case #2026-207923 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -7725,6 +8367,11 @@
       <c r="L103" t="n">
         <v>504.5</v>
       </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>Motor vehicle theft on Jul 11, 2026, 504 m from Northgate Station (113XX BLOCK OF 8TH AVE NE). Case #2026-203002 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -7779,6 +8426,11 @@
       <c r="L104" t="n">
         <v>145.2</v>
       </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 10, 2026, 145 m from Northgate Station (3XX BLOCK OF NE NORTHGATE WAY). Case #2026-700469 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -7833,6 +8485,11 @@
       <c r="L105" t="n">
         <v>338.4</v>
       </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>Credit card/automated teller machine fraud on Jul 10, 2026, 338 m from Northgate Station (5XX BLOCK OF NE NORTHGATE WAY). Case #2026-912276 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -7887,6 +8544,11 @@
       <c r="L106" t="n">
         <v>539.1</v>
       </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jul 10, 2026, 539 m from Northgate Station (8XX BLOCK OF NE NORTHGATE WAY). Case #2026-200722 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -7941,6 +8603,11 @@
       <c r="L107" t="n">
         <v>338.4</v>
       </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>Credit card/automated teller machine fraud on Jul 10, 2026, 338 m from Northgate Station (5XX BLOCK OF NE NORTHGATE WAY). Case #2026-912316 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -7995,6 +8662,11 @@
       <c r="L108" t="n">
         <v>504.5</v>
       </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>Intimidation on Jul 09, 2026, 504 m from Northgate Station (113XX BLOCK OF 8TH AVE NE). Case #2026-200096 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -8049,6 +8721,11 @@
       <c r="L109" t="n">
         <v>661.7</v>
       </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>Destruction/damage/vandalism of property on Jul 08, 2026, 662 m from Northgate Station (100XX BLOCK OF 1ST AVE NE). Case #2026-912125 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -8103,6 +8780,11 @@
       <c r="L110" t="n">
         <v>145.2</v>
       </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>All other larceny on Jul 07, 2026, 145 m from Northgate Station (4XX BLOCK OF NE NORTHGATE WAY). Case #2026-198224 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -8157,6 +8839,11 @@
       <c r="L111" t="n">
         <v>338.4</v>
       </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>Simple assault on Jul 07, 2026, 338 m from Northgate Station (5XX BLOCK OF NE NORTHGATE WAY). Case #2026-196771 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -8211,6 +8898,11 @@
       <c r="L112" t="n">
         <v>891.2</v>
       </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>Identity theft on Jul 07, 2026, 891 m from Northgate Station (113XX BLOCK OF 12TH AVE NE). Case #2026-913095 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -8265,6 +8957,11 @@
       <c r="L113" t="n">
         <v>446.4</v>
       </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>Destruction/damage/vandalism of property on Jul 06, 2026, 446 m from Northgate Station (106XX BLOCK OF 8TH AVE NE). Case #2026-197607 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -8319,6 +9016,11 @@
       <c r="L114" t="n">
         <v>316.5</v>
       </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>Theft from building on Jul 06, 2026, 316 m from Northgate Station (113XX BLOCK OF 3RD AVE NE). Case #2026-912274 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -8373,6 +9075,11 @@
       <c r="L115" t="n">
         <v>175.6</v>
       </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>Theft of motor vehicle parts or accessories on Jul 06, 2026, 176 m from Northgate Station (3RD AVE NE / NE 112TH ST). Case #2026-912004 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -8427,6 +9134,11 @@
       <c r="L116" t="n">
         <v>446.4</v>
       </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>Theft from building on Jul 03, 2026, 446 m from Northgate Station (107XX BLOCK OF 8TH AVE NE). Case #2026-196223 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -8481,6 +9193,11 @@
       <c r="L117" t="n">
         <v>798.3</v>
       </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>Aggravated assault on Jul 02, 2026, 798 m from Northgate Station (117XX BLOCK OF 5TH AVE NE). Case #2026-191308 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -8535,6 +9252,11 @@
       <c r="L118" t="n">
         <v>438.6</v>
       </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>Theft from motor vehicle on Jul 01, 2026, 439 m from Northgate Station (NE NORTHGATE WAY / 8TH AVE NE). Case #2026-911816 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -8589,6 +9311,11 @@
       <c r="L119" t="n">
         <v>338.4</v>
       </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>Not reportable to nibrs on Jul 01, 2026, 338 m from Northgate Station (5XX BLOCK OF NE NORTHGATE WAY). Case #2026-190746 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -8643,6 +9370,11 @@
       <c r="L120" t="n">
         <v>880.9</v>
       </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>Drug/narcotic violations on Jul 01, 2026, 881 m from Northgate Station (100XX BLOCK OF COLLEGE WAY N). Case #2026-190665 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -8697,6 +9429,11 @@
       <c r="L121" t="n">
         <v>504.5</v>
       </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>Not reportable to nibrs on Jul 01, 2026, 504 m from Northgate Station (110XX BLOCK OF 8TH AVE NE). Case #2026-190986 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -8751,6 +9488,11 @@
       <c r="L122" t="n">
         <v>145.2</v>
       </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>Burglary/breaking &amp; entering on Jun 30, 2026, 145 m from Northgate Station (3XX BLOCK OF NE NORTHGATE WAY). Case #2026-189518 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -8805,6 +9547,11 @@
       <c r="L123" t="n">
         <v>661.7</v>
       </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>Not reportable to nibrs on Jun 30, 2026, 662 m from Northgate Station (102XX BLOCK OF 1ST AVE NE). Case #2026-911710 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -8859,6 +9606,11 @@
       <c r="L124" t="n">
         <v>145.2</v>
       </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jun 30, 2026, 145 m from Northgate Station (3XX BLOCK OF NE NORTHGATE WAY). Case #2026-700460 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -8913,6 +9665,11 @@
       <c r="L125" t="n">
         <v>627</v>
       </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>Impersonation on Jun 30, 2026, 627 m from Northgate Station (3XX BLOCK OF NE THORNTON PL). Case #2026-190221 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -8967,6 +9724,11 @@
       <c r="L126" t="n">
         <v>706.5</v>
       </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>Theft from motor vehicle on Jun 29, 2026, 706 m from Northgate Station (8XX BLOCK OF NE 105TH ST). Case #2026-187728 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -9021,6 +9783,11 @@
       <c r="L127" t="n">
         <v>706.5</v>
       </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>Not reportable to nibrs on Jun 29, 2026, 706 m from Northgate Station (8XX BLOCK OF NE 105TH ST). Case #2026-187728 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -9075,6 +9842,11 @@
       <c r="L128" t="n">
         <v>539</v>
       </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>Shoplifting on Jun 29, 2026, 539 m from Northgate Station (8XX BLOCK OF NE NORTHGATE WAY). Case #2026-187628 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -9129,6 +9901,11 @@
       <c r="L129" t="n">
         <v>25.7</v>
       </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>Theft-shoplift on Jun 29, 2026, 26 m from Cherry Creek Shopping Center (3000 E 1ST AVE). Victims: 1. Case #DP20266008929 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -9183,6 +9960,11 @@
       <c r="L130" t="n">
         <v>25.7</v>
       </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>Disturbing-the-peace on Jul 06, 2026, 26 m from Cherry Creek Shopping Center (3000 E 1ST AVE). Victims: 1. Case #DP2026370716 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -9237,6 +10019,11 @@
       <c r="L131" t="n">
         <v>25.7</v>
       </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>Theft-shoplift on Jul 05, 2026, 26 m from Cherry Creek Shopping Center (3000 E 1ST AVE). Victims: 1. Case #DP20266009170 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -9291,6 +10078,11 @@
       <c r="L132" t="n">
         <v>25.7</v>
       </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>Theft-shoplift on Jul 02, 2026, 26 m from Cherry Creek Shopping Center (3000 E 1ST AVE). Victims: 1. Case #DP20266009209 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -9345,6 +10137,11 @@
       <c r="L133" t="n">
         <v>25.7</v>
       </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>Theft-shoplift on Jul 08, 2026, 26 m from Cherry Creek Shopping Center (3000 E 1ST AVE). Victims: 1. Case #DP2026376323 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -9399,6 +10196,11 @@
       <c r="L134" t="n">
         <v>25.7</v>
       </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>Theft-shoplift on Jul 09, 2026, 26 m from Cherry Creek Shopping Center (3000 E 1ST AVE). Victims: 1. Case #DP20266009395 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -9453,6 +10255,11 @@
       <c r="L135" t="n">
         <v>25.7</v>
       </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>Theft-shoplift on Jul 09, 2026, 26 m from Cherry Creek Shopping Center (3000 E 1ST AVE). Victims: 1. Case #DP2026380800 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -9507,6 +10314,11 @@
       <c r="L136" t="n">
         <v>25.7</v>
       </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>Theft-from-bldg on Jul 15, 2026, 26 m from Cherry Creek Shopping Center (3000 E 1ST AVE). Victims: 1. Case #DP20266009631 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -9561,6 +10373,11 @@
       <c r="L137" t="n">
         <v>25.7</v>
       </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>Theft-shoplift on Jul 21, 2026, 26 m from Cherry Creek Shopping Center (3000 E 1ST AVE). Victims: 1. Case #DP20266009882 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -9615,6 +10432,11 @@
       <c r="L138" t="n">
         <v>100.4</v>
       </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>Theft-other on Jul 20, 2026, 100 m from Cherry Creek Shopping Center (3030 E 1ST AVE). Victims: 1. Case #DP2026399148 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -9669,6 +10491,11 @@
       <c r="L139" t="n">
         <v>144.7</v>
       </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>Theft-shoplift on Jul 07, 2026, 145 m from Cherry Creek Shopping Center (15 S STEELE ST). Victims: 1. Case #DP20266009249 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -9723,6 +10550,11 @@
       <c r="L140" t="n">
         <v>160</v>
       </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>Theft-shoplift on Jul 15, 2026, 160 m from Cherry Creek Shopping Center (3110 E 1ST AVE). Victims: 1. Case #DP2026388611 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -9777,6 +10609,11 @@
       <c r="L141" t="n">
         <v>171.5</v>
       </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>Theft-other on Jul 02, 2026, 171 m from Cherry Creek Shopping Center (100 BLOCK N FILLMORE ST). Victims: 1. Case #DP2026361915 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -9831,6 +10668,11 @@
       <c r="L142" t="n">
         <v>247.6</v>
       </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>Theft-shoplift on Jul 02, 2026, 248 m from Cherry Creek Shopping Center (2810 E 1ST AVE). Victims: 1. Case #DP2026361616 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -9885,6 +10727,11 @@
       <c r="L143" t="n">
         <v>247.6</v>
       </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>Theft-other on Jul 05, 2026, 248 m from Cherry Creek Shopping Center (2810 E 1ST AVE). Victims: 1. Case #DP2026368528 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -9939,6 +10786,11 @@
       <c r="L144" t="n">
         <v>247.6</v>
       </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>Theft-bicycle on Jul 03, 2026, 248 m from Cherry Creek Shopping Center (2810 E 1ST AVE). Victims: 1. Case #DP20266009015 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -9993,6 +10845,11 @@
       <c r="L145" t="n">
         <v>247.6</v>
       </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>Theft-shoplift on Jul 07, 2026, 248 m from Cherry Creek Shopping Center (2810 E 1ST AVE). Victims: 1. Case #DP20266009264 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -10047,6 +10904,11 @@
       <c r="L146" t="n">
         <v>247.6</v>
       </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>Theft-shoplift on Jul 09, 2026, 248 m from Cherry Creek Shopping Center (2810 E 1ST AVE). Victims: 1. Case #DP2026377178 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -10101,6 +10963,11 @@
       <c r="L147" t="n">
         <v>247.6</v>
       </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>Drug-methampetamine-possess on Jul 18, 2026, 248 m from Cherry Creek Shopping Center (2810 E 1ST AVE). Victims: 1. Case #DP2026395041 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -10155,6 +11022,11 @@
       <c r="L148" t="n">
         <v>247.6</v>
       </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>Criminal-trespassing on Jul 18, 2026, 248 m from Cherry Creek Shopping Center (2810 E 1ST AVE). Victims: 1. Case #DP2026395041 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -10209,6 +11081,11 @@
       <c r="L149" t="n">
         <v>247.6</v>
       </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>Theft-shoplift on Jul 17, 2026, 248 m from Cherry Creek Shopping Center (2810 E 1ST AVE). Victims: 1. Case #DP2026395355 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -10263,6 +11140,11 @@
       <c r="L150" t="n">
         <v>247.6</v>
       </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>Theft-shoplift on Jul 18, 2026, 248 m from Cherry Creek Shopping Center (2810 E 1ST AVE). Victims: 1. Case #DP2026395041 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -10317,6 +11199,11 @@
       <c r="L151" t="n">
         <v>247.6</v>
       </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>Theft-shoplift on Jul 21, 2026, 248 m from Cherry Creek Shopping Center (2810 E 1ST AVE). Victims: 1. Case #DP2026407757 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -10371,6 +11258,11 @@
       <c r="L152" t="n">
         <v>247.6</v>
       </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>Theft-shoplift on Jul 22, 2026, 248 m from Cherry Creek Shopping Center (2810 E 1ST AVE). Victims: 1. Case #DP2026405696 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -10425,6 +11317,11 @@
       <c r="L153" t="n">
         <v>247.6</v>
       </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>Theft-shoplift on Jul 23, 2026, 248 m from Cherry Creek Shopping Center (2810 E 1ST AVE). Victims: 1. Case #DP2026405563 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -10479,6 +11376,11 @@
       <c r="L154" t="n">
         <v>336.5</v>
       </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>Theft-other on Jul 09, 2026, 336 m from Cherry Creek Shopping Center (3200 BLK E 1ST AVE). Victims: 1. Case #DP20266009457 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -10533,6 +11435,11 @@
       <c r="L155" t="n">
         <v>448.9</v>
       </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>Fraud-criminal-impersonation on Jun 30, 2026, 449 m from Cherry Creek Shopping Center (101 N COOK ST). Victims: 1. Case #DP2026361832 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -10587,6 +11494,11 @@
       <c r="L156" t="n">
         <v>482.2</v>
       </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>Theft-shoplift on Jul 14, 2026, 482 m from Cherry Creek Shopping Center (2375 E 1ST AVE). Victims: 1. Case #DP2026387192 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -10641,6 +11553,11 @@
       <c r="L157" t="n">
         <v>493.3</v>
       </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>Violation-of-court-order on Jul 01, 2026, 493 m from Cherry Creek Shopping Center (250 N STEELE ST). Victims: 1. Case #DP2026359687 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -10695,6 +11612,11 @@
       <c r="L158" t="n">
         <v>497.1</v>
       </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>Theft-items-from-vehicle on Jul 15, 2026, 497 m from Cherry Creek Shopping Center (3498 E ELLSWORTH AVE). Victims: 1. Case #DP20266009661 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -10749,6 +11671,11 @@
       <c r="L159" t="n">
         <v>497.7</v>
       </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>Robbery-bank on Jul 01, 2026, 498 m from Cherry Creek Shopping Center (3410 E 1ST AVE). Victims: 1. Case #DP2026357948 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -10803,6 +11730,11 @@
       <c r="L160" t="n">
         <v>499.1</v>
       </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>Theft-bicycle on Jul 17, 2026, 499 m from Cherry Creek Shopping Center (3300 E BAYAUD AVE). Victims: 1. Case #DP20266009730 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -10857,6 +11789,11 @@
       <c r="L161" t="n">
         <v>504.6</v>
       </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>Theft-bicycle on Jul 20, 2026, 505 m from Cherry Creek Shopping Center (2817 E 3RD AVE). Victims: 1. Case #DP20266009841 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -10911,6 +11848,11 @@
       <c r="L162" t="n">
         <v>527.7</v>
       </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>Theft-of-motor-vehicle on Jul 20, 2026, 528 m from Cherry Creek Shopping Center (E 3RD AVE / N CLAYTON ST). Victims: 1. Case #DP2026399087 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -10965,6 +11907,11 @@
       <c r="L163" t="n">
         <v>546.3</v>
       </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>Theft-of-motor-vehicle on Jul 23, 2026, 546 m from Cherry Creek Shopping Center (3333 E BAYAUD AVE). Victims: 1. Case #DP2026409948 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -11019,6 +11966,11 @@
       <c r="L164" t="n">
         <v>566.4</v>
       </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>Harassment on Jul 22, 2026, 566 m from Cherry Creek Shopping Center (300 BLOCK N ST PAUL ST). Victims: 1. Case #DP2026403380 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -11073,6 +12025,11 @@
       <c r="L165" t="n">
         <v>566.4</v>
       </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>Disturbing-the-peace on Jul 22, 2026, 566 m from Cherry Creek Shopping Center (300 BLOCK N ST PAUL ST). Victims: 1. Case #DP2026403380 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -11127,6 +12084,11 @@
       <c r="L166" t="n">
         <v>566.4</v>
       </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>Assault-simple on Jul 22, 2026, 566 m from Cherry Creek Shopping Center (300 BLOCK N ST PAUL ST). Victims: 1. Case #DP2026403380 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -11181,6 +12143,11 @@
       <c r="L167" t="n">
         <v>628.1</v>
       </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>Criminal-mischief-mtr-veh on Jul 21, 2026, 628 m from Cherry Creek Shopping Center (2445 E 3RD AVE). Victims: 1. Case #DP2026401106 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -11235,6 +12202,11 @@
       <c r="L168" t="n">
         <v>627.3</v>
       </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>Theft-other on Jul 10, 2026, 627 m from Cherry Creek Shopping Center (106 S MADISON ST). Victims: 1. Case #DP20266009356 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -11289,6 +12261,11 @@
       <c r="L169" t="n">
         <v>637.1</v>
       </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>Theft-items-from-vehicle on Jul 14, 2026, 637 m from Cherry Creek Shopping Center (3131 E ALAMEDA AVE). Victims: 1. Case #DP2026386904 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -11343,6 +12320,11 @@
       <c r="L170" t="n">
         <v>642</v>
       </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>Theft-parts-from-vehicle on Jul 06, 2026, 642 m from Cherry Creek Shopping Center (2605 E ALAMEDA AVE). Victims: 1. Case #DP20266009245 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -11397,6 +12379,11 @@
       <c r="L171" t="n">
         <v>690.8</v>
       </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>Theft-other on Jun 30, 2026, 691 m from Cherry Creek Shopping Center (191 N UNIVERSITY BLVD). Victims: 1. Case #DP20266009219 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -11451,6 +12438,11 @@
       <c r="L172" t="n">
         <v>709.2</v>
       </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>Criminal-mischief-other on Jul 21, 2026, 709 m from Cherry Creek Shopping Center (443 N MILWAUKEE ST). Victims: 1. Case #DP20266009856 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -11505,6 +12497,11 @@
       <c r="L173" t="n">
         <v>769.8</v>
       </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>Theft-other on Jun 30, 2026, 770 m from Cherry Creek Shopping Center (400 BLK N CLAYTON ST). Victims: 1. Case #DP20266008959 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -11559,6 +12556,11 @@
       <c r="L174" t="n">
         <v>779.5</v>
       </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>Burglary-residence-no-force on Jul 26, 2026, 779 m from Cherry Creek Shopping Center (100 BLK N GARFIELD ST). Victims: 1. Case #DP2026411500 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -11613,6 +12615,11 @@
       <c r="L175" t="n">
         <v>794.9</v>
       </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>Theft-from-bldg on Jul 18, 2026, 795 m from Cherry Creek Shopping Center (00 BLK N GARFIELD ST). Victims: 1. Case #DP20266009776 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -11667,6 +12674,11 @@
       <c r="L176" t="n">
         <v>868.5</v>
       </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>Theft-parts-from-vehicle on Jul 19, 2026, 869 m from Cherry Creek Shopping Center (2450 E 5TH AVE). Victims: 1. Case #DP20266009826 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -11721,6 +12733,11 @@
       <c r="L177" t="n">
         <v>952.3</v>
       </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>Theft-other on Jul 16, 2026, 952 m from Cherry Creek Shopping Center (3689 E CHERRY CREEK S DR). Victims: 1. Case #DP20266009658 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -11775,9 +12792,14 @@
       <c r="L178" t="n">
         <v>962</v>
       </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>Criminal-mischief-other on Jul 04, 2026, 962 m from Cherry Creek Shopping Center (3030 E 6TH AVE). Victims: 1. Case #DP20266009033 (use for a records request — full narratives are not published in open data).</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L178"/>
+  <autoFilter ref="A1:M178"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11815,7 +12837,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-29 07:35:12.335477+00:00</t>
+          <t>2026-07-29 07:43:40.709434+00:00</t>
         </is>
       </c>
     </row>
@@ -11837,7 +12859,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-29 07:35:12.335477+00:00</t>
+          <t>2026-06-29 07:43:40.709434+00:00</t>
         </is>
       </c>
     </row>

--- a/reports/2026-07-29/blotter_report.xlsx
+++ b/reports/2026-07-29/blotter_report.xlsx
@@ -12837,7 +12837,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-29 07:43:40.709434+00:00</t>
+          <t>2026-07-29 07:53:08.662629+00:00</t>
         </is>
       </c>
     </row>
@@ -12859,7 +12859,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-29 07:43:40.709434+00:00</t>
+          <t>2026-06-29 07:53:08.662629+00:00</t>
         </is>
       </c>
     </row>

--- a/reports/2026-07-29/blotter_report.xlsx
+++ b/reports/2026-07-29/blotter_report.xlsx
@@ -12837,7 +12837,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-29 07:53:08.662629+00:00</t>
+          <t>2026-07-29 07:57:37.243492+00:00</t>
         </is>
       </c>
     </row>
@@ -12859,7 +12859,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-29 07:53:08.662629+00:00</t>
+          <t>2026-06-29 07:57:37.243492+00:00</t>
         </is>
       </c>
     </row>
